--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43.27146670347973</v>
+        <v>7.031613339315457</v>
       </c>
       <c r="D2" t="n">
-        <v>43.43924237019247</v>
+        <v>7.058876885156277</v>
       </c>
       <c r="E2" t="n">
-        <v>12.23826293829986</v>
+        <v>1.988717727473727</v>
       </c>
       <c r="F2" t="n">
-        <v>12.49411527575073</v>
+        <v>2.030293732309493</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.0303707969056</v>
+        <v>4.392435254497161</v>
       </c>
       <c r="D3" t="n">
-        <v>27.24836379951309</v>
+        <v>4.427859117420877</v>
       </c>
       <c r="E3" t="n">
-        <v>12.23826293829986</v>
+        <v>1.988717727473727</v>
       </c>
       <c r="F3" t="n">
-        <v>12.49411527575073</v>
+        <v>2.030293732309493</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.27317823599815</v>
+        <v>4.9193914633497</v>
       </c>
       <c r="D4" t="n">
-        <v>30.25665807603466</v>
+        <v>4.916706937355634</v>
       </c>
       <c r="E4" t="n">
-        <v>12.23826293829986</v>
+        <v>1.988717727473727</v>
       </c>
       <c r="F4" t="n">
-        <v>12.49411527575073</v>
+        <v>2.030293732309493</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.41023121518298</v>
+        <v>3.641662572467235</v>
       </c>
       <c r="D5" t="n">
-        <v>22.40989514030046</v>
+        <v>3.641607960298824</v>
       </c>
       <c r="E5" t="n">
-        <v>12.23826293829986</v>
+        <v>1.988717727473727</v>
       </c>
       <c r="F5" t="n">
-        <v>12.49411527575073</v>
+        <v>2.030293732309493</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>13.82054277434782</v>
+        <v>2.24583820083152</v>
       </c>
       <c r="D6" t="n">
-        <v>13.57737026967667</v>
+        <v>2.206322668822459</v>
       </c>
       <c r="E6" t="n">
-        <v>12.23826293829986</v>
+        <v>1.988717727473727</v>
       </c>
       <c r="F6" t="n">
-        <v>12.49411527575073</v>
+        <v>2.030293732309493</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>6.694844625206468</v>
+        <v>1.087912251596051</v>
       </c>
       <c r="D7" t="n">
-        <v>6.26658770267674</v>
+        <v>1.01832050168497</v>
       </c>
       <c r="E7" t="n">
-        <v>12.23826293829986</v>
+        <v>1.988717727473727</v>
       </c>
       <c r="F7" t="n">
-        <v>12.49411527575073</v>
+        <v>2.030293732309493</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>29.60864594308041</v>
+        <v>4.811404965750568</v>
       </c>
       <c r="D8" t="n">
-        <v>27.56379297177769</v>
+        <v>4.479116357913876</v>
       </c>
       <c r="E8" t="n">
-        <v>12.23826293829986</v>
+        <v>1.988717727473727</v>
       </c>
       <c r="F8" t="n">
-        <v>12.49411527575073</v>
+        <v>2.030293732309493</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>36.51664408244254</v>
+        <v>5.933954663396912</v>
       </c>
       <c r="D9" t="n">
-        <v>37.84073648922522</v>
+        <v>6.149119679499099</v>
       </c>
       <c r="E9" t="n">
-        <v>12.23826293829986</v>
+        <v>1.988717727473727</v>
       </c>
       <c r="F9" t="n">
-        <v>12.49411527575073</v>
+        <v>2.030293732309493</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>31.80510637964115</v>
+        <v>5.168329786691687</v>
       </c>
       <c r="D10" t="n">
-        <v>30.04037678095903</v>
+        <v>4.881561226905843</v>
       </c>
       <c r="E10" t="n">
-        <v>12.23826293829986</v>
+        <v>1.988717727473727</v>
       </c>
       <c r="F10" t="n">
-        <v>12.49411527575073</v>
+        <v>2.030293732309493</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>55.33418602783082</v>
+        <v>8.991805229522509</v>
       </c>
       <c r="D11" t="n">
-        <v>54.93299073147931</v>
+        <v>8.926610993865388</v>
       </c>
       <c r="E11" t="n">
-        <v>12.23826293829986</v>
+        <v>1.988717727473727</v>
       </c>
       <c r="F11" t="n">
-        <v>12.49411527575073</v>
+        <v>2.030293732309493</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>48.34704165099256</v>
+        <v>7.856394268286291</v>
       </c>
       <c r="D12" t="n">
-        <v>46.95845025459422</v>
+        <v>7.630748166371561</v>
       </c>
       <c r="E12" t="n">
-        <v>12.23826293829986</v>
+        <v>1.988717727473727</v>
       </c>
       <c r="F12" t="n">
-        <v>12.49411527575073</v>
+        <v>2.030293732309493</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>41.2880451985305</v>
+        <v>6.709307344761207</v>
       </c>
       <c r="D13" t="n">
-        <v>43.51643271538491</v>
+        <v>7.071420316250048</v>
       </c>
       <c r="E13" t="n">
-        <v>12.23826293829986</v>
+        <v>1.988717727473727</v>
       </c>
       <c r="F13" t="n">
-        <v>12.49411527575073</v>
+        <v>2.030293732309493</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>29.48367458281409</v>
+        <v>4.791097119707289</v>
       </c>
       <c r="D14" t="n">
-        <v>30.98161242487865</v>
+        <v>5.03451201904278</v>
       </c>
       <c r="E14" t="n">
-        <v>12.23826293829986</v>
+        <v>1.988717727473727</v>
       </c>
       <c r="F14" t="n">
-        <v>12.49411527575073</v>
+        <v>2.030293732309493</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>35.1129214342295</v>
+        <v>5.705849733062294</v>
       </c>
       <c r="D15" t="n">
-        <v>36.38859573584838</v>
+        <v>5.913146807075362</v>
       </c>
       <c r="E15" t="n">
-        <v>12.23826293829986</v>
+        <v>1.988717727473727</v>
       </c>
       <c r="F15" t="n">
-        <v>12.49411527575073</v>
+        <v>2.030293732309493</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>42.01086512499099</v>
+        <v>6.826765582811035</v>
       </c>
       <c r="D16" t="n">
-        <v>44.14113588216011</v>
+        <v>7.172934580851018</v>
       </c>
       <c r="E16" t="n">
-        <v>12.23826293829986</v>
+        <v>1.988717727473727</v>
       </c>
       <c r="F16" t="n">
-        <v>12.49411527575073</v>
+        <v>2.030293732309493</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
